--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1757</v>
+        <v>1895</v>
       </c>
       <c r="C2">
-        <v>1947</v>
+        <v>2029</v>
       </c>
       <c r="D2">
-        <v>2083</v>
+        <v>2115</v>
       </c>
       <c r="E2">
-        <v>2118</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1759</v>
+        <v>1917</v>
       </c>
       <c r="C3">
-        <v>1952</v>
+        <v>2048</v>
       </c>
       <c r="D3">
-        <v>2089</v>
+        <v>2131</v>
       </c>
       <c r="E3">
-        <v>2121</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1790</v>
+        <v>1961</v>
       </c>
       <c r="C4">
-        <v>1971</v>
+        <v>2072</v>
       </c>
       <c r="D4">
-        <v>2100</v>
+        <v>2144</v>
       </c>
       <c r="E4">
-        <v>2129</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1733</v>
+        <v>1869</v>
       </c>
       <c r="C5">
-        <v>1936</v>
+        <v>2008</v>
       </c>
       <c r="D5">
-        <v>2081</v>
+        <v>2108</v>
       </c>
       <c r="E5">
-        <v>2127</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1246</v>
+        <v>1808</v>
       </c>
       <c r="C6">
-        <v>1617</v>
+        <v>1991</v>
       </c>
       <c r="D6">
-        <v>1886</v>
+        <v>2089</v>
       </c>
       <c r="E6">
-        <v>2047</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1334</v>
+        <v>1603</v>
       </c>
       <c r="C7">
-        <v>1665</v>
+        <v>1850</v>
       </c>
       <c r="D7">
-        <v>1901</v>
+        <v>2038</v>
       </c>
       <c r="E7">
-        <v>2056</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1393</v>
+        <v>1954</v>
       </c>
       <c r="C8">
-        <v>1704</v>
+        <v>2041</v>
       </c>
       <c r="D8">
-        <v>1924</v>
+        <v>2105</v>
       </c>
       <c r="E8">
-        <v>2072</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1322</v>
+        <v>1639</v>
       </c>
       <c r="C9">
-        <v>1654</v>
+        <v>1859</v>
       </c>
       <c r="D9">
-        <v>1896</v>
+        <v>2023</v>
       </c>
       <c r="E9">
-        <v>2050</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1526</v>
+        <v>1631</v>
       </c>
       <c r="C10">
-        <v>1812</v>
+        <v>1868</v>
       </c>
       <c r="D10">
-        <v>2003</v>
+        <v>2025</v>
       </c>
       <c r="E10">
-        <v>2078</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1514</v>
+        <v>1621</v>
       </c>
       <c r="C11">
-        <v>1809</v>
+        <v>1859</v>
       </c>
       <c r="D11">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="E11">
-        <v>2074</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1136</v>
+        <v>1234</v>
       </c>
       <c r="C12">
-        <v>1563</v>
+        <v>1632</v>
       </c>
       <c r="D12">
-        <v>1878</v>
+        <v>1910</v>
       </c>
       <c r="E12">
-        <v>2000</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1399</v>
+        <v>1514</v>
       </c>
       <c r="C13">
-        <v>1732</v>
+        <v>1798</v>
       </c>
       <c r="D13">
-        <v>1956</v>
+        <v>1983</v>
       </c>
       <c r="E13">
-        <v>2049</v>
+        <v>2057</v>
       </c>
     </row>
   </sheetData>
